--- a/artfynd/A 61163-2025 artfynd.xlsx
+++ b/artfynd/A 61163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130244648</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>130244365</v>
       </c>
       <c r="B3" t="n">
-        <v>97707</v>
+        <v>97794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61163-2025 artfynd.xlsx
+++ b/artfynd/A 61163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130244648</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>130244365</v>
       </c>
       <c r="B3" t="n">
-        <v>97794</v>
+        <v>97797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61163-2025 artfynd.xlsx
+++ b/artfynd/A 61163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130244648</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>130244365</v>
       </c>
       <c r="B3" t="n">
-        <v>97797</v>
+        <v>97823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61163-2025 artfynd.xlsx
+++ b/artfynd/A 61163-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>130244365</v>
       </c>
       <c r="B3" t="n">
-        <v>97823</v>
+        <v>97824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61163-2025 artfynd.xlsx
+++ b/artfynd/A 61163-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>130244365</v>
       </c>
       <c r="B3" t="n">
-        <v>97824</v>
+        <v>97825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61163-2025 artfynd.xlsx
+++ b/artfynd/A 61163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130244648</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>130244365</v>
       </c>
       <c r="B3" t="n">
-        <v>97825</v>
+        <v>97827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61163-2025 artfynd.xlsx
+++ b/artfynd/A 61163-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>130244365</v>
       </c>
       <c r="B3" t="n">
-        <v>97827</v>
+        <v>97831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61163-2025 artfynd.xlsx
+++ b/artfynd/A 61163-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>130244648</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -784,17 +784,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130244365</v>
+        <v>130245749</v>
       </c>
       <c r="B3" t="n">
-        <v>97831</v>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,27 +802,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -863,19 +868,14 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:57</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett tiotal självgallrade tallar som dött</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130245749</v>
+        <v>130244365</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,32 +913,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -980,14 +974,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett tiotal självgallrade tallar som dött</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61163-2025 artfynd.xlsx
+++ b/artfynd/A 61163-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130244648</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130245749</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,8 +1026,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130244365</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>